--- a/GameData/DataTables/Core/UIGroupTable.xlsx
+++ b/GameData/DataTables/Core/UIGroupTable.xlsx
@@ -10,9 +10,76 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="145621" fullCalcOnLoad="1"/>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>UIGroup</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Depth</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>备注</t>
+  </si>
+  <si>
+    <t>每个组的起始Order,用于控制显示顺序</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>Default interface</t>
+  </si>
+  <si>
+    <t>Default</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Dialog interface</t>
+  </si>
+  <si>
+    <t>Dialog</t>
+  </si>
+  <si>
+    <t>200</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>Overlay interface</t>
+  </si>
+  <si>
+    <t>Overlay</t>
+  </si>
+  <si>
+    <t>500</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -20,17 +87,17 @@
   <numFmts count="0"/>
   <fonts count="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -51,10 +118,10 @@
     </xf>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -425,147 +492,130 @@
   <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
-    <col width="2.5" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
-    <col width="11.625" bestFit="1" customWidth="1" style="1" min="2" max="2"/>
-    <col width="9" bestFit="1" customWidth="1" style="1" min="3" max="3"/>
-    <col width="9.5" bestFit="1" customWidth="1" style="1" min="4" max="4"/>
-    <col width="36.375" bestFit="1" customWidth="1" style="1" min="5" max="5"/>
+    <col min="1" max="1" bestFit="1" width="2.5" customWidth="1" style="1"/>
+    <col min="2" max="2" bestFit="1" width="11.625" customWidth="1" style="1"/>
+    <col min="3" max="3" bestFit="1" width="9" customWidth="1" style="1"/>
+    <col min="4" max="4" bestFit="1" width="9.5" customWidth="1" style="1"/>
+    <col min="5" max="5" bestFit="1" width="36.375" customWidth="1" style="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>UIGroup</t>
-        </is>
-      </c>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Depth</t>
-        </is>
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
+      <c r="A3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>每个组的起始Order,用于控制显示顺序</t>
-        </is>
+      <c r="A4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="5">
-      <c r="B5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Default interface</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Default</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>1</v>
+      <c r="A5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="6">
-      <c r="B6" t="n">
-        <v>2</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Dialog interface</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Dialog</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>200</v>
+      <c r="A6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="7">
-      <c r="B7" t="n">
+      <c r="A7" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Overlay interface</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Overlay</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>500</v>
+      <c r="B7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
@@ -575,11 +625,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
@@ -589,10 +639,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
+  <headerFooter/>
 </worksheet>
 </file>